--- a/output/pdf_financials_xlsx/H.xlsx
+++ b/output/pdf_financials_xlsx/H.xlsx
@@ -3034,31 +3034,31 @@
         <v>155</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>295</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>371</v>
       </c>
     </row>
     <row r="65">
@@ -3154,7 +3154,7 @@
         <v>598</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>659</v>
       </c>
       <c r="E67" s="3" t="n">
         <v>53</v>
@@ -3163,22 +3163,22 @@
         <v>55</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>619</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>683</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>644</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>794</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>944</v>
       </c>
     </row>
     <row r="68">
@@ -3194,31 +3194,31 @@
         <v>753</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>53</v>
+        <v>230</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>55</v>
+        <v>234</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0</v>
+        <v>874</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0</v>
+        <v>978</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0</v>
+        <v>978</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0</v>
+        <v>1142</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="69">
@@ -3474,31 +3474,31 @@
         <v>2244</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>2163</v>
+        <v>1323</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>905104</v>
+        <v>904927</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>2973</v>
+        <v>2794</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>3087</v>
+        <v>2286</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>2978</v>
+        <v>2104</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>3652</v>
+        <v>2674</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>2720</v>
+        <v>1742</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>3501</v>
+        <v>2359</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>3590</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="76">
@@ -4687,37 +4687,37 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>-23</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
     </row>
     <row r="107">
@@ -18434,7 +18434,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -18554,7 +18558,11 @@
           <t>Changes in non-cash balances related to operations (Note 28)</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -19809,7 +19817,11 @@
           <t>Changes in non-cash balances related to operations (Note 29)</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -20741,7 +20753,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -20879,7 +20895,11 @@
           <t>Changes in non-cash balances related to operations (Note 29)</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -21021,7 +21041,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -21159,7 +21183,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -21368,7 +21396,11 @@
           <t>Changes in non-cash balances related to operations (Note 30)</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -22831,7 +22863,11 @@
           <t>Changes in non-cash balances related to operations (Note 27)</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -23247,7 +23283,11 @@
           <t>Changes in non-cash balances related to operations (Note 24)</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E258" s="5" t="n">
         <v>-55</v>
       </c>
